--- a/Matlab/Output/Source_data/normalization_EF_planetary_boundaries.xlsx
+++ b/Matlab/Output/Source_data/normalization_EF_planetary_boundaries.xlsx
@@ -146,13 +146,13 @@
     <col min="16" max="16" width="15.453125" customWidth="true"/>
     <col min="17" max="17" width="15.453125" customWidth="true"/>
     <col min="18" max="18" width="15.453125" customWidth="true"/>
-    <col min="19" max="19" width="15.453125" customWidth="true"/>
+    <col min="19" max="19" width="14.453125" customWidth="true"/>
     <col min="20" max="20" width="15.453125" customWidth="true"/>
     <col min="21" max="21" width="15.453125" customWidth="true"/>
     <col min="22" max="22" width="15.453125" customWidth="true"/>
-    <col min="23" max="23" width="15.453125" customWidth="true"/>
-    <col min="24" max="24" width="14.453125" customWidth="true"/>
-    <col min="25" max="25" width="14.453125" customWidth="true"/>
+    <col min="23" max="23" width="14.453125" customWidth="true"/>
+    <col min="24" max="24" width="15.453125" customWidth="true"/>
+    <col min="25" max="25" width="15.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -237,76 +237,76 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.034663123867706973</v>
+        <v>0.038284152440008754</v>
       </c>
       <c r="C2" s="0">
-        <v>0.035359555009201078</v>
+        <v>0.039053335162451401</v>
       </c>
       <c r="D2" s="0">
-        <v>0.036306206834439927</v>
+        <v>0.040098877477776892</v>
       </c>
       <c r="E2" s="0">
-        <v>0.037511942186354987</v>
+        <v>0.041430568071827135</v>
       </c>
       <c r="F2" s="0">
-        <v>0.039159302404351483</v>
+        <v>0.043250017177166984</v>
       </c>
       <c r="G2" s="0">
-        <v>0.041187102869896783</v>
+        <v>0.045489648620574814</v>
       </c>
       <c r="H2" s="0">
-        <v>0.043438816855925572</v>
+        <v>0.047976584357279625</v>
       </c>
       <c r="I2" s="0">
-        <v>0.046260464917647598</v>
+        <v>0.051092991434128786</v>
       </c>
       <c r="J2" s="0">
-        <v>0.048158001290435362</v>
+        <v>0.053188750951751101</v>
       </c>
       <c r="K2" s="0">
-        <v>0.05003056440640398</v>
+        <v>0.055256928420662613</v>
       </c>
       <c r="L2" s="0">
-        <v>0.05232527295176178</v>
+        <v>0.057791350075535819</v>
       </c>
       <c r="M2" s="0">
-        <v>0.054748890693137243</v>
+        <v>0.060468147222303363</v>
       </c>
       <c r="N2" s="0">
-        <v>0.056869076996633482</v>
+        <v>0.062809815444534428</v>
       </c>
       <c r="O2" s="0">
-        <v>0.058552514175983054</v>
+        <v>0.064669110234103003</v>
       </c>
       <c r="P2" s="0">
-        <v>0.060060178545407697</v>
+        <v>0.066334270384345417</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.060963818226532268</v>
+        <v>0.067332307359750376</v>
       </c>
       <c r="R2" s="0">
-        <v>0.061575539176182803</v>
+        <v>0.06800793077374355</v>
       </c>
       <c r="S2" s="0">
-        <v>0.062010795720380193</v>
+        <v>0.068488655706446119</v>
       </c>
       <c r="T2" s="0">
-        <v>0.061797069717882222</v>
+        <v>0.068252603154135644</v>
       </c>
       <c r="U2" s="0">
-        <v>0.061902816742563871</v>
+        <v>0.068369396874991301</v>
       </c>
       <c r="V2" s="0">
-        <v>0.0612890680122452</v>
+        <v>0.067691533851420238</v>
       </c>
       <c r="W2" s="0">
-        <v>0.062983167024235662</v>
+        <v>0.069562604245163195</v>
       </c>
       <c r="X2" s="0">
-        <v>0.062728157249783728</v>
+        <v>0.069280955276764658</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.061391950412147914</v>
+        <v>0.067805163698986828</v>
       </c>
     </row>
     <row r="3">
@@ -314,76 +314,76 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>0.94308297192160884</v>
+        <v>1.0416006473744222</v>
       </c>
       <c r="C3" s="0">
-        <v>0.96315665685135932</v>
+        <v>1.0637712981448575</v>
       </c>
       <c r="D3" s="0">
-        <v>0.98789751586061547</v>
+        <v>1.091096671975043</v>
       </c>
       <c r="E3" s="0">
-        <v>1.0179203288461478</v>
+        <v>1.1242557707741794</v>
       </c>
       <c r="F3" s="0">
-        <v>1.0570759419613007</v>
+        <v>1.1675017132663696</v>
       </c>
       <c r="G3" s="0">
-        <v>1.1022326147407002</v>
+        <v>1.2173756066571699</v>
       </c>
       <c r="H3" s="0">
-        <v>1.1536527643941661</v>
+        <v>1.2741672811564013</v>
       </c>
       <c r="I3" s="0">
-        <v>1.2189616717014673</v>
+        <v>1.3462985804756891</v>
       </c>
       <c r="J3" s="0">
-        <v>1.2637331039505435</v>
+        <v>1.3957469897916768</v>
       </c>
       <c r="K3" s="0">
-        <v>1.3089843862671677</v>
+        <v>1.4457253759558122</v>
       </c>
       <c r="L3" s="0">
-        <v>1.3678110403711061</v>
+        <v>1.5106972637131351</v>
       </c>
       <c r="M3" s="0">
-        <v>1.4247932979842466</v>
+        <v>1.573632083008798</v>
       </c>
       <c r="N3" s="0">
-        <v>1.477191683706204</v>
+        <v>1.6315041834647717</v>
       </c>
       <c r="O3" s="0">
-        <v>1.5203900217881221</v>
+        <v>1.6792151678121436</v>
       </c>
       <c r="P3" s="0">
-        <v>1.5578475540683561</v>
+        <v>1.7205856421328094</v>
       </c>
       <c r="Q3" s="0">
-        <v>1.5931336313249189</v>
+        <v>1.7595578238050651</v>
       </c>
       <c r="R3" s="0">
-        <v>1.6218346257301837</v>
+        <v>1.7912570223304081</v>
       </c>
       <c r="S3" s="0">
-        <v>1.6463976995987204</v>
+        <v>1.81838603897551</v>
       </c>
       <c r="T3" s="0">
-        <v>1.649271596862397</v>
+        <v>1.8215601533848009</v>
       </c>
       <c r="U3" s="0">
-        <v>1.6577478996316666</v>
+        <v>1.830921919756028</v>
       </c>
       <c r="V3" s="0">
-        <v>1.641783128393574</v>
+        <v>1.8132894138664359</v>
       </c>
       <c r="W3" s="0">
-        <v>1.6775862864242812</v>
+        <v>1.8528326923404888</v>
       </c>
       <c r="X3" s="0">
-        <v>1.6530779769566926</v>
+        <v>1.8257641609731181</v>
       </c>
       <c r="Y3" s="0">
-        <v>1.6052943961086883</v>
+        <v>1.7729889437048687</v>
       </c>
     </row>
     <row r="4">
@@ -391,76 +391,76 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>0.0013766893756677031</v>
+        <v>0.0015205030603056657</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0013956993404292256</v>
+        <v>0.0015414988710579487</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0014157684703573546</v>
+        <v>0.0015636644909957013</v>
       </c>
       <c r="E4" s="0">
-        <v>0.001439801663287893</v>
+        <v>0.0015902082735262208</v>
       </c>
       <c r="F4" s="0">
-        <v>0.0014691858914083684</v>
+        <v>0.0016226620786993981</v>
       </c>
       <c r="G4" s="0">
-        <v>0.001494084219751651</v>
+        <v>0.0016501613716492656</v>
       </c>
       <c r="H4" s="0">
-        <v>0.0015152503241168927</v>
+        <v>0.0016735385597288135</v>
       </c>
       <c r="I4" s="0">
-        <v>0.001517482518653662</v>
+        <v>0.0016760039369477734</v>
       </c>
       <c r="J4" s="0">
-        <v>0.0015111224131332756</v>
+        <v>0.0016689794330338645</v>
       </c>
       <c r="K4" s="0">
-        <v>0.0015054712256540252</v>
+        <v>0.00166273790316632</v>
       </c>
       <c r="L4" s="0">
-        <v>0.0015017027163570027</v>
+        <v>0.0016585757224883918</v>
       </c>
       <c r="M4" s="0">
-        <v>0.0014957747605498222</v>
+        <v>0.001652028512125994</v>
       </c>
       <c r="N4" s="0">
-        <v>0.001496863799187029</v>
+        <v>0.0016532313154670607</v>
       </c>
       <c r="O4" s="0">
-        <v>0.0014965929373914283</v>
+        <v>0.001652932158521122</v>
       </c>
       <c r="P4" s="0">
-        <v>0.0014974183363992636</v>
+        <v>0.0016538437815346854</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.0015062903204244936</v>
+        <v>0.0016636425633803013</v>
       </c>
       <c r="R4" s="0">
-        <v>0.0015128610057862791</v>
+        <v>0.001670899645026664</v>
       </c>
       <c r="S4" s="0">
-        <v>0.0015269458789279871</v>
+        <v>0.0016864558722297666</v>
       </c>
       <c r="T4" s="0">
-        <v>0.0015329506766785172</v>
+        <v>0.0016930879517079488</v>
       </c>
       <c r="U4" s="0">
-        <v>0.0015628006247524681</v>
+        <v>0.0017260561275351176</v>
       </c>
       <c r="V4" s="0">
-        <v>0.0015742279166503677</v>
+        <v>0.00173867715346069</v>
       </c>
       <c r="W4" s="0">
-        <v>0.0016761414004279117</v>
+        <v>0.0018512368686070433</v>
       </c>
       <c r="X4" s="0">
-        <v>0.0017568793928991839</v>
+        <v>0.0019404090281408268</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.0017861636318561335</v>
+        <v>0.0019727523989401898</v>
       </c>
     </row>
     <row r="5">
@@ -468,76 +468,76 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>0.9411061161034211</v>
+        <v>1.03941728243062</v>
       </c>
       <c r="C5" s="0">
-        <v>0.96114953465084552</v>
+        <v>1.0615545050888286</v>
       </c>
       <c r="D5" s="0">
-        <v>0.98585696024579361</v>
+        <v>1.0888429529358039</v>
       </c>
       <c r="E5" s="0">
-        <v>1.0158396288027107</v>
+        <v>1.1219577136818961</v>
       </c>
       <c r="F5" s="0">
-        <v>1.0549452577791008</v>
+        <v>1.1651484505210907</v>
       </c>
       <c r="G5" s="0">
-        <v>1.1000542701524583</v>
+        <v>1.2149697047366907</v>
       </c>
       <c r="H5" s="0">
-        <v>1.1514280051802963</v>
+        <v>1.2717101159796222</v>
       </c>
       <c r="I5" s="0">
-        <v>1.2167048267414611</v>
+        <v>1.3438059777659017</v>
       </c>
       <c r="J5" s="0">
-        <v>1.261462951467299</v>
+        <v>1.3932396894092216</v>
       </c>
       <c r="K5" s="0">
-        <v>1.3066996988587263</v>
+        <v>1.4432020222801203</v>
       </c>
       <c r="L5" s="0">
-        <v>1.3655041419735545</v>
+        <v>1.5081493788123816</v>
       </c>
       <c r="M5" s="0">
-        <v>1.4224654737380868</v>
+        <v>1.5710610862736609</v>
       </c>
       <c r="N5" s="0">
-        <v>1.474836165963118</v>
+        <v>1.6289026002752234</v>
       </c>
       <c r="O5" s="0">
-        <v>1.5180105008455274</v>
+        <v>1.6765870739667026</v>
       </c>
       <c r="P5" s="0">
-        <v>1.5554422776387133</v>
+        <v>1.7179291022939811</v>
       </c>
       <c r="Q5" s="0">
-        <v>1.5906893785148759</v>
+        <v>1.7568582359797227</v>
       </c>
       <c r="R5" s="0">
-        <v>1.6193565944840604</v>
+        <v>1.7885201274579274</v>
       </c>
       <c r="S5" s="0">
-        <v>1.6438725161933092</v>
+        <v>1.8155970662677787</v>
       </c>
       <c r="T5" s="0">
-        <v>1.6467143122143859</v>
+        <v>1.8187357260287842</v>
       </c>
       <c r="U5" s="0">
-        <v>1.6551253340596139</v>
+        <v>1.8280253920071856</v>
       </c>
       <c r="V5" s="0">
-        <v>1.6391201175468275</v>
+        <v>1.8103482157910595</v>
       </c>
       <c r="W5" s="0">
-        <v>1.6747384336871489</v>
+        <v>1.8496873431581364</v>
       </c>
       <c r="X5" s="0">
-        <v>1.6500857905268984</v>
+        <v>1.8224594005065093</v>
       </c>
       <c r="Y5" s="0">
-        <v>1.6022489640969688</v>
+        <v>1.7696253754405851</v>
       </c>
     </row>
     <row r="6">
@@ -545,76 +545,76 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>0.00060026110509797052</v>
+        <v>0.00066296643485118801</v>
       </c>
       <c r="C6" s="0">
-        <v>0.00061150755594431853</v>
+        <v>0.00067538772844993877</v>
       </c>
       <c r="D6" s="0">
-        <v>0.00062487904122269079</v>
+        <v>0.00069015604485155003</v>
       </c>
       <c r="E6" s="0">
-        <v>0.00064099633888593755</v>
+        <v>0.00070795701059877105</v>
       </c>
       <c r="F6" s="0">
-        <v>0.00066160451294717951</v>
+        <v>0.00073071798506494853</v>
       </c>
       <c r="G6" s="0">
-        <v>0.00068437381213568591</v>
+        <v>0.00075586584318679099</v>
       </c>
       <c r="H6" s="0">
-        <v>0.00070961213850768881</v>
+        <v>0.000783740651523284</v>
       </c>
       <c r="I6" s="0">
-        <v>0.00073945429119918126</v>
+        <v>0.00081670021763565858</v>
       </c>
       <c r="J6" s="0">
-        <v>0.00075912403808979045</v>
+        <v>0.00083842473361668991</v>
       </c>
       <c r="K6" s="0">
-        <v>0.00077929646780350499</v>
+        <v>0.00086070444438922909</v>
       </c>
       <c r="L6" s="0">
-        <v>0.00080527147527931664</v>
+        <v>0.00088939289005932</v>
       </c>
       <c r="M6" s="0">
-        <v>0.00083210879740694226</v>
+        <v>0.00091903373072148634</v>
       </c>
       <c r="N6" s="0">
-        <v>0.00085871084678329642</v>
+        <v>0.00094841472123543657</v>
       </c>
       <c r="O6" s="0">
-        <v>0.00088296943338947887</v>
+        <v>0.00097520744283648825</v>
       </c>
       <c r="P6" s="0">
-        <v>0.00090790578266187788</v>
+        <v>0.0010027487285118747</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.00093800331030284578</v>
+        <v>0.0010359903469151044</v>
       </c>
       <c r="R6" s="0">
-        <v>0.00096521121238861234</v>
+        <v>0.0010660404795863471</v>
       </c>
       <c r="S6" s="0">
-        <v>0.00099826194820451086</v>
+        <v>0.0011025438083993951</v>
       </c>
       <c r="T6" s="0">
-        <v>0.0010243644634641267</v>
+        <v>0.0011313730817528499</v>
       </c>
       <c r="U6" s="0">
-        <v>0.0010598071816980202</v>
+        <v>0.0011705182676551155</v>
       </c>
       <c r="V6" s="0">
-        <v>0.0010888099068092037</v>
+        <v>0.0012025507167087522</v>
       </c>
       <c r="W6" s="0">
-        <v>0.0011717280719380557</v>
+        <v>0.0012941307971987333</v>
       </c>
       <c r="X6" s="0">
-        <v>0.001235313308363483</v>
+        <v>0.0013643583650756411</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0012592626635974029</v>
+        <v>0.0013908095519367739</v>
       </c>
     </row>
     <row r="7">
@@ -622,76 +622,76 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>0.46912099492783843</v>
+        <v>0.51812697987551626</v>
       </c>
       <c r="C7" s="0">
-        <v>0.4774621800772953</v>
+        <v>0.52733951377785282</v>
       </c>
       <c r="D7" s="0">
-        <v>0.48747747569715966</v>
+        <v>0.5384010414608742</v>
       </c>
       <c r="E7" s="0">
-        <v>0.49963816232411501</v>
+        <v>0.55183207503933551</v>
       </c>
       <c r="F7" s="0">
-        <v>0.51530492153566254</v>
+        <v>0.56913543754598406</v>
       </c>
       <c r="G7" s="0">
-        <v>0.53273093604918542</v>
+        <v>0.58838183318544468</v>
       </c>
       <c r="H7" s="0">
-        <v>0.55188097062620289</v>
+        <v>0.60953234592561312</v>
       </c>
       <c r="I7" s="0">
-        <v>0.5743899383797153</v>
+        <v>0.63439267749963857</v>
       </c>
       <c r="J7" s="0">
-        <v>0.5888440987921526</v>
+        <v>0.65035676898585393</v>
       </c>
       <c r="K7" s="0">
-        <v>0.60357558792708865</v>
+        <v>0.6666271599022261</v>
       </c>
       <c r="L7" s="0">
-        <v>0.6223211606380038</v>
+        <v>0.6873309593052721</v>
       </c>
       <c r="M7" s="0">
-        <v>0.64133416591147574</v>
+        <v>0.70833012819179064</v>
       </c>
       <c r="N7" s="0">
-        <v>0.65976332434469187</v>
+        <v>0.72868445959859218</v>
       </c>
       <c r="O7" s="0">
-        <v>0.6757313288925334</v>
+        <v>0.74632053656053743</v>
       </c>
       <c r="P7" s="0">
-        <v>0.69141241725012192</v>
+        <v>0.76363972508487155</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.70837660470849695</v>
+        <v>0.7823760496341533</v>
       </c>
       <c r="R7" s="0">
-        <v>0.72440097011217863</v>
+        <v>0.8000743750998649</v>
       </c>
       <c r="S7" s="0">
-        <v>0.74315177647746944</v>
+        <v>0.8207839548827377</v>
       </c>
       <c r="T7" s="0">
-        <v>0.75556647190177284</v>
+        <v>0.83449553188699888</v>
       </c>
       <c r="U7" s="0">
-        <v>0.77333233100623056</v>
+        <v>0.85411727344666322</v>
       </c>
       <c r="V7" s="0">
-        <v>0.78364250496351318</v>
+        <v>0.86550448346760833</v>
       </c>
       <c r="W7" s="0">
-        <v>0.82492345187970217</v>
+        <v>0.91109777940478254</v>
       </c>
       <c r="X7" s="0">
-        <v>0.84809610067235319</v>
+        <v>0.93669112241109842</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.84997337281633256</v>
+        <v>0.93876450082920582</v>
       </c>
     </row>
     <row r="8">
@@ -699,76 +699,76 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>0.41517925693889773</v>
+        <v>0.45855030329180169</v>
       </c>
       <c r="C8" s="0">
-        <v>0.42365768785647839</v>
+        <v>0.46791442012499734</v>
       </c>
       <c r="D8" s="0">
-        <v>0.43393597809068712</v>
+        <v>0.47926641574001722</v>
       </c>
       <c r="E8" s="0">
-        <v>0.44635272570083173</v>
+        <v>0.49298025930847733</v>
       </c>
       <c r="F8" s="0">
-        <v>0.46242030184013855</v>
+        <v>0.51072630945116926</v>
       </c>
       <c r="G8" s="0">
-        <v>0.48070306487719577</v>
+        <v>0.53091895249761256</v>
       </c>
       <c r="H8" s="0">
-        <v>0.50134204286534734</v>
+        <v>0.55371394877434743</v>
       </c>
       <c r="I8" s="0">
-        <v>0.52696709187383906</v>
+        <v>0.58201587811770206</v>
       </c>
       <c r="J8" s="0">
-        <v>0.54421431098989725</v>
+        <v>0.60106480078045588</v>
       </c>
       <c r="K8" s="0">
-        <v>0.56166878396705</v>
+        <v>0.62034262775207127</v>
       </c>
       <c r="L8" s="0">
-        <v>0.58451204285081226</v>
+        <v>0.64557217165210268</v>
       </c>
       <c r="M8" s="0">
-        <v>0.60646934724183221</v>
+        <v>0.66982321122042676</v>
       </c>
       <c r="N8" s="0">
-        <v>0.62672019695836101</v>
+        <v>0.69218953401770855</v>
       </c>
       <c r="O8" s="0">
-        <v>0.64312038059644261</v>
+        <v>0.71030293697702429</v>
       </c>
       <c r="P8" s="0">
-        <v>0.65714616571794937</v>
+        <v>0.72579390362307494</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.67027798155818585</v>
+        <v>0.74029751389664589</v>
       </c>
       <c r="R8" s="0">
-        <v>0.68081925924529518</v>
+        <v>0.75193996953411157</v>
       </c>
       <c r="S8" s="0">
-        <v>0.68972626014830118</v>
+        <v>0.76177742624042011</v>
       </c>
       <c r="T8" s="0">
-        <v>0.68964559433827743</v>
+        <v>0.76168833380375933</v>
       </c>
       <c r="U8" s="0">
-        <v>0.69226639224557829</v>
+        <v>0.76458290923153949</v>
       </c>
       <c r="V8" s="0">
-        <v>0.68419387059273651</v>
+        <v>0.75566710433431894</v>
       </c>
       <c r="W8" s="0">
-        <v>0.69786798624535018</v>
+        <v>0.770769664914979</v>
       </c>
       <c r="X8" s="0">
-        <v>0.6873919288556346</v>
+        <v>0.75919924271042427</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.66743230403482523</v>
+        <v>0.73715456715834171</v>
       </c>
     </row>
     <row r="9">
@@ -776,76 +776,76 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>0.30977842561983299</v>
+        <v>0.34213894034242825</v>
       </c>
       <c r="C9" s="0">
-        <v>0.3154183810449484</v>
+        <v>0.34836806481701521</v>
       </c>
       <c r="D9" s="0">
-        <v>0.32210830224785975</v>
+        <v>0.35575683808861613</v>
       </c>
       <c r="E9" s="0">
-        <v>0.33018652566764428</v>
+        <v>0.36467894037887166</v>
       </c>
       <c r="F9" s="0">
-        <v>0.34051879356688342</v>
+        <v>0.37609055235057842</v>
       </c>
       <c r="G9" s="0">
-        <v>0.3518924896696492</v>
+        <v>0.3886523836807973</v>
       </c>
       <c r="H9" s="0">
-        <v>0.36399768015951189</v>
+        <v>0.40202212380572</v>
       </c>
       <c r="I9" s="0">
-        <v>0.37754314347581314</v>
+        <v>0.41698259258663511</v>
       </c>
       <c r="J9" s="0">
-        <v>0.38568360366267301</v>
+        <v>0.42597343310969332</v>
       </c>
       <c r="K9" s="0">
-        <v>0.39373488555648406</v>
+        <v>0.43486577946995042</v>
       </c>
       <c r="L9" s="0">
-        <v>0.40355457636984804</v>
+        <v>0.44571126879882228</v>
       </c>
       <c r="M9" s="0">
-        <v>0.41305099410087009</v>
+        <v>0.45619971483259569</v>
       </c>
       <c r="N9" s="0">
-        <v>0.42189846685082738</v>
+        <v>0.46597142487122117</v>
       </c>
       <c r="O9" s="0">
-        <v>0.4289828013330973</v>
+        <v>0.47379581318343283</v>
       </c>
       <c r="P9" s="0">
-        <v>0.43596767632916489</v>
+        <v>0.48151035213106019</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.44429502279029964</v>
+        <v>0.49070760170832223</v>
       </c>
       <c r="R9" s="0">
-        <v>0.45142126729661131</v>
+        <v>0.49857827810914657</v>
       </c>
       <c r="S9" s="0">
-        <v>0.46049007655370261</v>
+        <v>0.50859444622408378</v>
       </c>
       <c r="T9" s="0">
-        <v>0.46586697527960025</v>
+        <v>0.51453303419620045</v>
       </c>
       <c r="U9" s="0">
-        <v>0.47572099598150575</v>
+        <v>0.52541643963128326</v>
       </c>
       <c r="V9" s="0">
-        <v>0.48165500154498625</v>
+        <v>0.53197033172823271</v>
       </c>
       <c r="W9" s="0">
-        <v>0.50848621705173491</v>
+        <v>0.56160442785100229</v>
       </c>
       <c r="X9" s="0">
-        <v>0.52441157903148017</v>
+        <v>0.57919340765622085</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.52609989865333606</v>
+        <v>0.58105809492495264</v>
       </c>
     </row>
     <row r="10">
@@ -853,76 +853,76 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>0.033314810018929886</v>
+        <v>0.03679498911126311</v>
       </c>
       <c r="C10" s="0">
-        <v>0.033882158639667738</v>
+        <v>0.037421604910977339</v>
       </c>
       <c r="D10" s="0">
-        <v>0.034814133966096783</v>
+        <v>0.038450937570189192</v>
       </c>
       <c r="E10" s="0">
-        <v>0.036092681008005605</v>
+        <v>0.039863046012606894</v>
       </c>
       <c r="F10" s="0">
-        <v>0.037953251262890078</v>
+        <v>0.041917977805113422</v>
       </c>
       <c r="G10" s="0">
-        <v>0.040466571425846448</v>
+        <v>0.044693847995474732</v>
       </c>
       <c r="H10" s="0">
-        <v>0.043376651713663013</v>
+        <v>0.04790792523146286</v>
       </c>
       <c r="I10" s="0">
-        <v>0.047231224511025752</v>
+        <v>0.052165159897575142</v>
       </c>
       <c r="J10" s="0">
-        <v>0.049997934756705054</v>
+        <v>0.055220890166063699</v>
       </c>
       <c r="K10" s="0">
-        <v>0.052786577295144278</v>
+        <v>0.058300843849688887</v>
       </c>
       <c r="L10" s="0">
-        <v>0.056313617833499474</v>
+        <v>0.062196331115863361</v>
       </c>
       <c r="M10" s="0">
-        <v>0.060355548107218909</v>
+        <v>0.066660495261643735</v>
       </c>
       <c r="N10" s="0">
-        <v>0.06390014578036407</v>
+        <v>0.070575373741007016</v>
       </c>
       <c r="O10" s="0">
-        <v>0.066781262108424652</v>
+        <v>0.073757461342858405</v>
       </c>
       <c r="P10" s="0">
-        <v>0.069331864192673689</v>
+        <v>0.076574508051627924</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.070139386923428457</v>
+        <v>0.077466387371015785</v>
       </c>
       <c r="R10" s="0">
-        <v>0.07046593448498488</v>
+        <v>0.077827047208636077</v>
       </c>
       <c r="S10" s="0">
-        <v>0.070240567850332628</v>
+        <v>0.077578138003890199</v>
       </c>
       <c r="T10" s="0">
-        <v>0.06935138293910291</v>
+        <v>0.076596065793122489</v>
       </c>
       <c r="U10" s="0">
-        <v>0.068603086009696598</v>
+        <v>0.075769599205023935</v>
       </c>
       <c r="V10" s="0">
-        <v>0.066964053586338182</v>
+        <v>0.073959347844256382</v>
       </c>
       <c r="W10" s="0">
-        <v>0.067616660665718975</v>
+        <v>0.074680128493046061</v>
       </c>
       <c r="X10" s="0">
-        <v>0.065877647358273853</v>
+        <v>0.072759451902802072</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.063381383805453051</v>
+        <v>0.070002420114456454</v>
       </c>
     </row>
     <row r="11">
@@ -930,76 +930,76 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>0.012506717099088325</v>
+        <v>0.013813211578187615</v>
       </c>
       <c r="C11" s="0">
-        <v>0.01271094228865623</v>
+        <v>0.014038770830127726</v>
       </c>
       <c r="D11" s="0">
-        <v>0.013042876569177374</v>
+        <v>0.014405380101814719</v>
       </c>
       <c r="E11" s="0">
-        <v>0.013497973365059934</v>
+        <v>0.014908017866807365</v>
       </c>
       <c r="F11" s="0">
-        <v>0.014158464246049522</v>
+        <v>0.015637505886108429</v>
       </c>
       <c r="G11" s="0">
-        <v>0.015045425901364625</v>
+        <v>0.016617122592038409</v>
       </c>
       <c r="H11" s="0">
-        <v>0.016068445188669737</v>
+        <v>0.017747009975926088</v>
       </c>
       <c r="I11" s="0">
-        <v>0.017408624079417224</v>
+        <v>0.019227188541080107</v>
       </c>
       <c r="J11" s="0">
-        <v>0.018365382071502977</v>
+        <v>0.020283892748035093</v>
       </c>
       <c r="K11" s="0">
-        <v>0.019330826453704278</v>
+        <v>0.021350190755150909</v>
       </c>
       <c r="L11" s="0">
-        <v>0.020556778693534752</v>
+        <v>0.022704210162431321</v>
       </c>
       <c r="M11" s="0">
-        <v>0.021955949458265112</v>
+        <v>0.024249543094655705</v>
       </c>
       <c r="N11" s="0">
-        <v>0.023180664091769582</v>
+        <v>0.025602195611016929</v>
       </c>
       <c r="O11" s="0">
-        <v>0.024165247251075071</v>
+        <v>0.02668963169740594</v>
       </c>
       <c r="P11" s="0">
-        <v>0.025030330117181955</v>
+        <v>0.02764508408091515</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.025278019459975282</v>
+        <v>0.027918647900305921</v>
       </c>
       <c r="R11" s="0">
-        <v>0.02538070402786384</v>
+        <v>0.028032059249648973</v>
       </c>
       <c r="S11" s="0">
-        <v>0.025275345202571232</v>
+        <v>0.027915694280819366</v>
       </c>
       <c r="T11" s="0">
-        <v>0.024927220397701951</v>
+        <v>0.027531203167190103</v>
       </c>
       <c r="U11" s="0">
-        <v>0.024634068765147066</v>
+        <v>0.027207427911630278</v>
       </c>
       <c r="V11" s="0">
-        <v>0.024024992390558716</v>
+        <v>0.026534725334062769</v>
       </c>
       <c r="W11" s="0">
-        <v>0.02422703300010607</v>
+        <v>0.026757871797275488</v>
       </c>
       <c r="X11" s="0">
-        <v>0.023552153289301159</v>
+        <v>0.026012491841743122</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.022627309033471963</v>
+        <v>0.024991035189175888</v>
       </c>
     </row>
     <row r="12">
@@ -1007,76 +1007,76 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>0.079477084549532562</v>
+        <v>0.08777953285440715</v>
       </c>
       <c r="C12" s="0">
-        <v>0.081109694342135358</v>
+        <v>0.089582690654425451</v>
       </c>
       <c r="D12" s="0">
-        <v>0.083059983336491713</v>
+        <v>0.09173671351303947</v>
       </c>
       <c r="E12" s="0">
-        <v>0.085409354472917406</v>
+        <v>0.094331508000355474</v>
       </c>
       <c r="F12" s="0">
-        <v>0.088432687611410418</v>
+        <v>0.097670668867470181</v>
       </c>
       <c r="G12" s="0">
-        <v>0.091781304956763718</v>
+        <v>0.10136909424315296</v>
       </c>
       <c r="H12" s="0">
-        <v>0.095389657601011882</v>
+        <v>0.10535438775613615</v>
       </c>
       <c r="I12" s="0">
-        <v>0.099482306383867763</v>
+        <v>0.10987456864012859</v>
       </c>
       <c r="J12" s="0">
-        <v>0.10206754818764549</v>
+        <v>0.11272987365210173</v>
       </c>
       <c r="K12" s="0">
-        <v>0.10462344101983892</v>
+        <v>0.11555276379845633</v>
       </c>
       <c r="L12" s="0">
-        <v>0.10768857225444282</v>
+        <v>0.118938089133878</v>
       </c>
       <c r="M12" s="0">
-        <v>0.11061666815846737</v>
+        <v>0.12217206395901128</v>
       </c>
       <c r="N12" s="0">
-        <v>0.11330261978809901</v>
+        <v>0.12513859928998028</v>
       </c>
       <c r="O12" s="0">
-        <v>0.11538466577171172</v>
+        <v>0.12743814292395714</v>
       </c>
       <c r="P12" s="0">
-        <v>0.11723916077728015</v>
+        <v>0.1294863648258083</v>
       </c>
       <c r="Q12" s="0">
-        <v>0.11905823793022564</v>
+        <v>0.13149546900491496</v>
       </c>
       <c r="R12" s="0">
-        <v>0.12061880034434122</v>
+        <v>0.13321905311066859</v>
       </c>
       <c r="S12" s="0">
-        <v>0.12230891813060354</v>
+        <v>0.13508572638621597</v>
       </c>
       <c r="T12" s="0">
-        <v>0.12270610808953115</v>
+        <v>0.13552440816784822</v>
       </c>
       <c r="U12" s="0">
-        <v>0.12387698123821195</v>
+        <v>0.13681759473357982</v>
       </c>
       <c r="V12" s="0">
-        <v>0.12325213649067183</v>
+        <v>0.13612747656484631</v>
       </c>
       <c r="W12" s="0">
-        <v>0.12753790486484942</v>
+        <v>0.140860950973725</v>
       </c>
       <c r="X12" s="0">
-        <v>0.12795658377542768</v>
+        <v>0.14132336651645477</v>
       </c>
       <c r="Y12" s="0">
-        <v>0.12603150752324943</v>
+        <v>0.13919719020937088</v>
       </c>
     </row>
     <row r="13">
@@ -1084,76 +1084,76 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>0.016066220572044154</v>
+        <v>0.017744552968232855</v>
       </c>
       <c r="C13" s="0">
-        <v>0.016453563426936761</v>
+        <v>0.018172358983635638</v>
       </c>
       <c r="D13" s="0">
-        <v>0.016945697681730498</v>
+        <v>0.018715903267277834</v>
       </c>
       <c r="E13" s="0">
-        <v>0.017541058778577708</v>
+        <v>0.019373457822243489</v>
       </c>
       <c r="F13" s="0">
-        <v>0.01831137346884866</v>
+        <v>0.020224242221874175</v>
       </c>
       <c r="G13" s="0">
-        <v>0.019204313606799247</v>
+        <v>0.021210461943200296</v>
       </c>
       <c r="H13" s="0">
-        <v>0.020095587864057851</v>
+        <v>0.022194841760234979</v>
       </c>
       <c r="I13" s="0">
-        <v>0.021184486248095744</v>
+        <v>0.023397490196806592</v>
       </c>
       <c r="J13" s="0">
-        <v>0.021918622885138503</v>
+        <v>0.02420831725993013</v>
       </c>
       <c r="K13" s="0">
-        <v>0.022667186110623572</v>
+        <v>0.025035077962307379</v>
       </c>
       <c r="L13" s="0">
-        <v>0.023592157707233406</v>
+        <v>0.026056675258109091</v>
       </c>
       <c r="M13" s="0">
-        <v>0.02440281629703752</v>
+        <v>0.026952018019116751</v>
       </c>
       <c r="N13" s="0">
-        <v>0.025180958379079299</v>
+        <v>0.02781144748665608</v>
       </c>
       <c r="O13" s="0">
-        <v>0.025903297991788223</v>
+        <v>0.02860924516790225</v>
       </c>
       <c r="P13" s="0">
-        <v>0.02668280865298716</v>
+        <v>0.029470186181062188</v>
       </c>
       <c r="Q13" s="0">
-        <v>0.027650887063862758</v>
+        <v>0.030539393376503989</v>
       </c>
       <c r="R13" s="0">
-        <v>0.028498812991005706</v>
+        <v>0.031475896548476288</v>
       </c>
       <c r="S13" s="0">
-        <v>0.029554012633307033</v>
+        <v>0.032641325957397563</v>
       </c>
       <c r="T13" s="0">
-        <v>0.030448241004329659</v>
+        <v>0.0336289684850321</v>
       </c>
       <c r="U13" s="0">
-        <v>0.031635043972713495</v>
+        <v>0.034939748953961229</v>
       </c>
       <c r="V13" s="0">
-        <v>0.032825600594648896</v>
+        <v>0.036254675195940819</v>
       </c>
       <c r="W13" s="0">
-        <v>0.035663810290039566</v>
+        <v>0.039389373991402701</v>
       </c>
       <c r="X13" s="0">
-        <v>0.037915610881614312</v>
+        <v>0.041876405380765251</v>
       </c>
       <c r="Y13" s="0">
-        <v>0.038863848214807498</v>
+        <v>0.042923698831633238</v>
       </c>
     </row>
     <row r="14">
@@ -1161,76 +1161,76 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>0.00063709123393334926</v>
+        <v>0.00070364396501552517</v>
       </c>
       <c r="C14" s="0">
-        <v>0.00064792630686777203</v>
+        <v>0.00071561090675750999</v>
       </c>
       <c r="D14" s="0">
-        <v>0.00066093853922837475</v>
+        <v>0.00072998244145182616</v>
       </c>
       <c r="E14" s="0">
-        <v>0.0006767640668327925</v>
+        <v>0.00074746115784113398</v>
       </c>
       <c r="F14" s="0">
-        <v>0.00069714982818162765</v>
+        <v>0.00076997648560163997</v>
       </c>
       <c r="G14" s="0">
-        <v>0.00071983274302324168</v>
+        <v>0.00079502893537201718</v>
       </c>
       <c r="H14" s="0">
-        <v>0.00074374527672662792</v>
+        <v>0.00082143945419949538</v>
       </c>
       <c r="I14" s="0">
-        <v>0.00077067297760309475</v>
+        <v>0.00085118011488397646</v>
       </c>
       <c r="J14" s="0">
-        <v>0.00078623621503444679</v>
+        <v>0.00086836914137091174</v>
       </c>
       <c r="K14" s="0">
-        <v>0.00080149875751981043</v>
+        <v>0.00088522606128851129</v>
       </c>
       <c r="L14" s="0">
-        <v>0.0008198743264790652</v>
+        <v>0.00090552120508146283</v>
       </c>
       <c r="M14" s="0">
-        <v>0.00083778263743595138</v>
+        <v>0.00092530027950167787</v>
       </c>
       <c r="N14" s="0">
-        <v>0.00085443302602859577</v>
+        <v>0.00094369002468157044</v>
       </c>
       <c r="O14" s="0">
-        <v>0.00086733894625560138</v>
+        <v>0.00095794414151290379</v>
       </c>
       <c r="P14" s="0">
-        <v>0.0008797717025560241</v>
+        <v>0.00097167566609422673</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.00089589340767341438</v>
+        <v>0.00098948149971333815</v>
       </c>
       <c r="R14" s="0">
-        <v>0.00090842124527645688</v>
+        <v>0.0010033180381156192</v>
       </c>
       <c r="S14" s="0">
-        <v>0.00092390027072286867</v>
+        <v>0.0010204140555454067</v>
       </c>
       <c r="T14" s="0">
-        <v>0.00093147925686743404</v>
+        <v>0.0010287847685257671</v>
       </c>
       <c r="U14" s="0">
-        <v>0.00094763690710605376</v>
+        <v>0.0010466303022165131</v>
       </c>
       <c r="V14" s="0">
-        <v>0.00095238711934354423</v>
+        <v>0.0010518767378844738</v>
       </c>
       <c r="W14" s="0">
-        <v>0.00099530879601675325</v>
+        <v>0.0010992821598253613</v>
       </c>
       <c r="X14" s="0">
-        <v>0.0010167435878532119</v>
+        <v>0.0011229561033890959</v>
       </c>
       <c r="Y14" s="0">
-        <v>0.0010132597848404952</v>
+        <v>0.001119108370388492</v>
       </c>
     </row>
     <row r="15">
@@ -1238,76 +1238,76 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>0.006921101218739201</v>
+        <v>0.0076441031432193888</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0070622050082643625</v>
+        <v>0.0077999471176015377</v>
       </c>
       <c r="D15" s="0">
-        <v>0.0072322597234192971</v>
+        <v>0.0079877663304047733</v>
       </c>
       <c r="E15" s="0">
-        <v>0.0074378851205316975</v>
+        <v>0.0082148720603624371</v>
       </c>
       <c r="F15" s="0">
-        <v>0.0077034843638690243</v>
+        <v>0.008508216709814248</v>
       </c>
       <c r="G15" s="0">
-        <v>0.0079999959234867621</v>
+        <v>0.0088357028819190577</v>
       </c>
       <c r="H15" s="0">
-        <v>0.0083338490626120639</v>
+        <v>0.0092044314627483179</v>
       </c>
       <c r="I15" s="0">
-        <v>0.0087359407424212106</v>
+        <v>0.0096485270158041623</v>
       </c>
       <c r="J15" s="0">
-        <v>0.0090110772172765884</v>
+        <v>0.0099524051886246759</v>
       </c>
       <c r="K15" s="0">
-        <v>0.0092925467459416475</v>
+        <v>0.010263277987734094</v>
       </c>
       <c r="L15" s="0">
-        <v>0.0096500428487922511</v>
+        <v>0.01065811935721009</v>
       </c>
       <c r="M15" s="0">
-        <v>0.010017457371485922</v>
+        <v>0.011063915258617061</v>
       </c>
       <c r="N15" s="0">
-        <v>0.010376920260842625</v>
+        <v>0.011460928871849962</v>
       </c>
       <c r="O15" s="0">
-        <v>0.010701665227742513</v>
+        <v>0.011819597809605552</v>
       </c>
       <c r="P15" s="0">
-        <v>0.011024312549661667</v>
+        <v>0.01217594997520541</v>
       </c>
       <c r="Q15" s="0">
-        <v>0.011367872353258158</v>
+        <v>0.012555399211902771</v>
       </c>
       <c r="R15" s="0">
-        <v>0.011705787985138612</v>
+        <v>0.012928614667386443</v>
       </c>
       <c r="S15" s="0">
-        <v>0.012097058068969293</v>
+        <v>0.01336075816350521</v>
       </c>
       <c r="T15" s="0">
-        <v>0.012385026327222834</v>
+        <v>0.013678808571741301</v>
       </c>
       <c r="U15" s="0">
-        <v>0.012744598805877106</v>
+        <v>0.014075943222344924</v>
       </c>
       <c r="V15" s="0">
-        <v>0.012984771103084828</v>
+        <v>0.01434120473983711</v>
       </c>
       <c r="W15" s="0">
-        <v>0.013792582514864796</v>
+        <v>0.015233402896858228</v>
       </c>
       <c r="X15" s="0">
-        <v>0.014257029737224099</v>
+        <v>0.015746367865884216</v>
       </c>
       <c r="Y15" s="0">
-        <v>0.014345367466957613</v>
+        <v>0.015843933657248819</v>
       </c>
     </row>
     <row r="16">
@@ -1315,76 +1315,76 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>0.47662847534562264</v>
+        <v>0.52641871739610924</v>
       </c>
       <c r="C16" s="0">
-        <v>0.48731142778196118</v>
+        <v>0.53821764761206625</v>
       </c>
       <c r="D16" s="0">
-        <v>0.49978552132516857</v>
+        <v>0.55199482766605401</v>
       </c>
       <c r="E16" s="0">
-        <v>0.51463742427757364</v>
+        <v>0.56839821123944878</v>
       </c>
       <c r="F16" s="0">
-        <v>0.53337712392818737</v>
+        <v>0.58909552406221066</v>
       </c>
       <c r="G16" s="0">
-        <v>0.55371042690418038</v>
+        <v>0.61155291346868057</v>
       </c>
       <c r="H16" s="0">
-        <v>0.57620745814653762</v>
+        <v>0.63640006160273654</v>
       </c>
       <c r="I16" s="0">
-        <v>0.60189151278922226</v>
+        <v>0.66476716051081031</v>
       </c>
       <c r="J16" s="0">
-        <v>0.61924702060671699</v>
+        <v>0.68393568408342864</v>
       </c>
       <c r="K16" s="0">
-        <v>0.6368449340022857</v>
+        <v>0.70337193575056933</v>
       </c>
       <c r="L16" s="0">
-        <v>0.65890169644291763</v>
+        <v>0.72773282309681631</v>
       </c>
       <c r="M16" s="0">
-        <v>0.68243526917742947</v>
+        <v>0.75372479339541476</v>
       </c>
       <c r="N16" s="0">
-        <v>0.70716850758904071</v>
+        <v>0.78104175055424008</v>
       </c>
       <c r="O16" s="0">
-        <v>0.7328428291598611</v>
+        <v>0.80939809964044596</v>
       </c>
       <c r="P16" s="0">
-        <v>0.76287068422138882</v>
+        <v>0.84256276722809531</v>
       </c>
       <c r="Q16" s="0">
-        <v>0.80348996223455438</v>
+        <v>0.8874252740637204</v>
       </c>
       <c r="R16" s="0">
-        <v>0.84252897834676321</v>
+        <v>0.9305424394309233</v>
       </c>
       <c r="S16" s="0">
-        <v>0.89430713209729029</v>
+        <v>0.98772951636065542</v>
       </c>
       <c r="T16" s="0">
-        <v>0.94493409803063622</v>
+        <v>1.0436451484532676</v>
       </c>
       <c r="U16" s="0">
-        <v>1.0083246316398446</v>
+        <v>1.1136576741912998</v>
       </c>
       <c r="V16" s="0">
-        <v>1.0815378633847148</v>
+        <v>1.1945190107356831</v>
       </c>
       <c r="W16" s="0">
-        <v>1.2280211761778059</v>
+        <v>1.3563044718006254</v>
       </c>
       <c r="X16" s="0">
-        <v>1.3639373496952671</v>
+        <v>1.5064189140495194</v>
       </c>
       <c r="Y16" s="0">
-        <v>1.4388230176654251</v>
+        <v>1.5891273952320917</v>
       </c>
     </row>
     <row r="17">
@@ -1392,76 +1392,76 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>0.0005888363265765461</v>
+        <v>0.00065034818485800057</v>
       </c>
       <c r="C17" s="0">
-        <v>0.00059798624658065163</v>
+        <v>0.00066045393682623006</v>
       </c>
       <c r="D17" s="0">
-        <v>0.00060903620043173607</v>
+        <v>0.00067265820668097596</v>
       </c>
       <c r="E17" s="0">
-        <v>0.00062253430016873394</v>
+        <v>0.00068756636412096637</v>
       </c>
       <c r="F17" s="0">
-        <v>0.00063992053097597422</v>
+        <v>0.00070676882011200509</v>
       </c>
       <c r="G17" s="0">
-        <v>0.00065946784423453933</v>
+        <v>0.00072835811262469442</v>
       </c>
       <c r="H17" s="0">
-        <v>0.00068113483697961942</v>
+        <v>0.00075228851359879689</v>
       </c>
       <c r="I17" s="0">
-        <v>0.00070751249138454187</v>
+        <v>0.0007814216680744879</v>
       </c>
       <c r="J17" s="0">
-        <v>0.00072424431468448005</v>
+        <v>0.00079990135490995201</v>
       </c>
       <c r="K17" s="0">
-        <v>0.00074159646018913318</v>
+        <v>0.00081906616493101993</v>
       </c>
       <c r="L17" s="0">
-        <v>0.00076506760254916185</v>
+        <v>0.00084498918316451566</v>
       </c>
       <c r="M17" s="0">
-        <v>0.00078843262479755553</v>
+        <v>0.00087079499561626189</v>
       </c>
       <c r="N17" s="0">
-        <v>0.00081069955014529522</v>
+        <v>0.00089538800020628811</v>
       </c>
       <c r="O17" s="0">
-        <v>0.00082894185278116722</v>
+        <v>0.00091553595621954103</v>
       </c>
       <c r="P17" s="0">
-        <v>0.00084539008786398639</v>
+        <v>0.00093370243024199341</v>
       </c>
       <c r="Q17" s="0">
-        <v>0.00086141006509673319</v>
+        <v>0.00095139590913341336</v>
       </c>
       <c r="R17" s="0">
-        <v>0.00087563904562441017</v>
+        <v>0.00096711129767330776</v>
       </c>
       <c r="S17" s="0">
-        <v>0.00088985944527844184</v>
+        <v>0.00098281720895212316</v>
       </c>
       <c r="T17" s="0">
-        <v>0.00089451686362564565</v>
+        <v>0.00098796115716238129</v>
       </c>
       <c r="U17" s="0">
-        <v>0.00090417687200066289</v>
+        <v>0.00099863028307879817</v>
       </c>
       <c r="V17" s="0">
-        <v>0.0009006075840931471</v>
+        <v>0.0009946881351386664</v>
       </c>
       <c r="W17" s="0">
-        <v>0.00092310383191434599</v>
+        <v>0.0010195344180127079</v>
       </c>
       <c r="X17" s="0">
-        <v>0.00089754008295658805</v>
+        <v>0.00099130019233321909</v>
       </c>
       <c r="Y17" s="0">
-        <v>0.00086321306204879713</v>
+        <v>0.00095338725331881122</v>
       </c>
     </row>
     <row r="18">
@@ -1469,76 +1469,76 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1.0167392491493921</v>
+        <v>1.1229513114494236</v>
       </c>
       <c r="C18" s="0">
-        <v>1.0352623007329405</v>
+        <v>1.1434093444064406</v>
       </c>
       <c r="D18" s="0">
-        <v>1.0601952791900222</v>
+        <v>1.1709469071396035</v>
       </c>
       <c r="E18" s="0">
-        <v>1.0911570393513701</v>
+        <v>1.2051430387505897</v>
       </c>
       <c r="F18" s="0">
-        <v>1.1315949842201762</v>
+        <v>1.2498052697608859</v>
       </c>
       <c r="G18" s="0">
-        <v>1.1795152148240811</v>
+        <v>1.3027314116862942</v>
       </c>
       <c r="H18" s="0">
-        <v>1.2330202090056088</v>
+        <v>1.3618257207094844</v>
       </c>
       <c r="I18" s="0">
-        <v>1.3005854764081817</v>
+        <v>1.4364490872231952</v>
       </c>
       <c r="J18" s="0">
-        <v>1.3443522850900014</v>
+        <v>1.4847879265552291</v>
       </c>
       <c r="K18" s="0">
-        <v>1.3877333936125997</v>
+        <v>1.5327007741691445</v>
       </c>
       <c r="L18" s="0">
-        <v>1.4414603766869163</v>
+        <v>1.5920402618047398</v>
       </c>
       <c r="M18" s="0">
-        <v>1.4729319187307359</v>
+        <v>1.626799428858642</v>
       </c>
       <c r="N18" s="0">
-        <v>1.4991126077554502</v>
+        <v>1.655715042276289</v>
       </c>
       <c r="O18" s="0">
-        <v>1.5163566486048323</v>
+        <v>1.6747604546597505</v>
       </c>
       <c r="P18" s="0">
-        <v>1.5307257280978321</v>
+        <v>1.6906305773824488</v>
       </c>
       <c r="Q18" s="0">
-        <v>1.5396903940867459</v>
+        <v>1.7005317230669288</v>
       </c>
       <c r="R18" s="0">
-        <v>1.5449307729912938</v>
+        <v>1.7063195298898453</v>
       </c>
       <c r="S18" s="0">
-        <v>1.5503180996102446</v>
+        <v>1.7122696350884186</v>
       </c>
       <c r="T18" s="0">
-        <v>1.5391585982490694</v>
+        <v>1.699944374015693</v>
       </c>
       <c r="U18" s="0">
-        <v>1.5410204382787529</v>
+        <v>1.7020007082280204</v>
       </c>
       <c r="V18" s="0">
-        <v>1.5236288087076606</v>
+        <v>1.6827922894997778</v>
       </c>
       <c r="W18" s="0">
-        <v>1.5657291989213102</v>
+        <v>1.7292906305862483</v>
       </c>
       <c r="X18" s="0">
-        <v>1.5597760850224776</v>
+        <v>1.722715634031827</v>
       </c>
       <c r="Y18" s="0">
-        <v>1.5274388958192249</v>
+        <v>1.6870003913530769</v>
       </c>
     </row>
     <row r="19">
@@ -1546,76 +1546,76 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>0.074812318046210649</v>
+        <v>0.082627468874489907</v>
       </c>
       <c r="C19" s="0">
-        <v>0.076133843744535107</v>
+        <v>0.084087045670889857</v>
       </c>
       <c r="D19" s="0">
-        <v>0.07807738864688317</v>
+        <v>0.086233619926559146</v>
       </c>
       <c r="E19" s="0">
-        <v>0.080636445821024388</v>
+        <v>0.08906000497285306</v>
       </c>
       <c r="F19" s="0">
-        <v>0.084224689541673892</v>
+        <v>0.093023088915244925</v>
       </c>
       <c r="G19" s="0">
-        <v>0.088838334124389129</v>
+        <v>0.098118690603736791</v>
       </c>
       <c r="H19" s="0">
-        <v>0.093947352541380577</v>
+        <v>0.10376141457291528</v>
       </c>
       <c r="I19" s="0">
-        <v>0.10073504976097677</v>
+        <v>0.11125817787859466</v>
       </c>
       <c r="J19" s="0">
-        <v>0.10548728664222744</v>
+        <v>0.11650684969153323</v>
       </c>
       <c r="K19" s="0">
-        <v>0.11029832944815016</v>
+        <v>0.12182047049732984</v>
       </c>
       <c r="L19" s="0">
-        <v>0.11644710750475312</v>
+        <v>0.12861157095720713</v>
       </c>
       <c r="M19" s="0">
-        <v>0.12315960177408899</v>
+        <v>0.13602527535501968</v>
       </c>
       <c r="N19" s="0">
-        <v>0.1290733879365257</v>
+        <v>0.14255683586308066</v>
       </c>
       <c r="O19" s="0">
-        <v>0.13382423343965863</v>
+        <v>0.14780397094978059</v>
       </c>
       <c r="P19" s="0">
-        <v>0.13798060428077516</v>
+        <v>0.1523945305163624</v>
       </c>
       <c r="Q19" s="0">
-        <v>0.13980393998266702</v>
+        <v>0.15440833810701554</v>
       </c>
       <c r="R19" s="0">
-        <v>0.14082337939210263</v>
+        <v>0.15553427164673744</v>
       </c>
       <c r="S19" s="0">
-        <v>0.14098417169331037</v>
+        <v>0.15571186086212699</v>
       </c>
       <c r="T19" s="0">
-        <v>0.13962148109109856</v>
+        <v>0.15420681893507071</v>
       </c>
       <c r="U19" s="0">
-        <v>0.13869020456346814</v>
+        <v>0.15317825807357202</v>
       </c>
       <c r="V19" s="0">
-        <v>0.13581381836032652</v>
+        <v>0.15000139472167998</v>
       </c>
       <c r="W19" s="0">
-        <v>0.1374939877339299</v>
+        <v>0.15185708033932829</v>
       </c>
       <c r="X19" s="0">
-        <v>0.13432583668621356</v>
+        <v>0.14835797338847606</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.12958133039293515</v>
+        <v>0.14311783972719136</v>
       </c>
     </row>
     <row r="20">
@@ -1623,76 +1623,76 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>0.0054554429757244071</v>
+        <v>0.0060253372231400216</v>
       </c>
       <c r="C20" s="0">
-        <v>0.0055562311013872875</v>
+        <v>0.006136654021410913</v>
       </c>
       <c r="D20" s="0">
-        <v>0.0056766127081075927</v>
+        <v>0.0062696111028396565</v>
       </c>
       <c r="E20" s="0">
-        <v>0.0058222654871010159</v>
+        <v>0.0064304792697012728</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0060087386253616639</v>
+        <v>0.006636432030288679</v>
       </c>
       <c r="G20" s="0">
-        <v>0.0062151418275031654</v>
+        <v>0.0068643968174512361</v>
       </c>
       <c r="H20" s="0">
-        <v>0.0064427041368552889</v>
+        <v>0.0071157310645919986</v>
       </c>
       <c r="I20" s="0">
-        <v>0.0067090141420462187</v>
+        <v>0.0074098607245136026</v>
       </c>
       <c r="J20" s="0">
-        <v>0.0068826707872663324</v>
+        <v>0.0076016581373261581</v>
       </c>
       <c r="K20" s="0">
-        <v>0.0070600205121513033</v>
+        <v>0.0077975344215469025</v>
       </c>
       <c r="L20" s="0">
-        <v>0.0072874064538778378</v>
+        <v>0.0080486738770961953</v>
       </c>
       <c r="M20" s="0">
-        <v>0.0075220827852570419</v>
+        <v>0.0083078653013565311</v>
       </c>
       <c r="N20" s="0">
-        <v>0.0077580745625742409</v>
+        <v>0.0085685095875403638</v>
       </c>
       <c r="O20" s="0">
-        <v>0.0079845107706885028</v>
+        <v>0.0088186000970532745</v>
       </c>
       <c r="P20" s="0">
-        <v>0.0082348204673171124</v>
+        <v>0.0090950580014105241</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.0086672008502171813</v>
+        <v>0.0095726063191614533</v>
       </c>
       <c r="R20" s="0">
-        <v>0.0089732984199467798</v>
+        <v>0.0099106798888076563</v>
       </c>
       <c r="S20" s="0">
-        <v>0.0093604894109067562</v>
+        <v>0.010338318176051568</v>
       </c>
       <c r="T20" s="0">
-        <v>0.0097074620104151393</v>
+        <v>0.010721536721003897</v>
       </c>
       <c r="U20" s="0">
-        <v>0.010157953484155765</v>
+        <v>0.011219088076139486</v>
       </c>
       <c r="V20" s="0">
-        <v>0.01055574974786758</v>
+        <v>0.011658439499229111</v>
       </c>
       <c r="W20" s="0">
-        <v>0.011565112023354919</v>
+        <v>0.012773243213096105</v>
       </c>
       <c r="X20" s="0">
-        <v>0.012420099976200213</v>
+        <v>0.013717546134149182</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.012813124841867123</v>
+        <v>0.01415162772262147</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1728,7 @@
         <v>1000000000000</v>
       </c>
       <c r="C2">
-        <v>780777435.13514268</v>
+        <v>706929191.90543818</v>
       </c>
     </row>
     <row r="3">
@@ -1739,7 +1739,7 @@
         <v>6810000000000</v>
       </c>
       <c r="C3">
-        <v>5317094333.2703209</v>
+        <v>4814187796.8760338</v>
       </c>
     </row>
     <row r="4">
@@ -1750,7 +1750,7 @@
         <v>6810000000000</v>
       </c>
       <c r="C4">
-        <v>5317094333.2703209</v>
+        <v>4814187796.8760338</v>
       </c>
     </row>
     <row r="5">
@@ -1761,7 +1761,7 @@
         <v>6810000000000</v>
       </c>
       <c r="C5">
-        <v>5317094333.2703209</v>
+        <v>4814187796.8760338</v>
       </c>
     </row>
     <row r="6">
@@ -1772,7 +1772,7 @@
         <v>6810000000000</v>
       </c>
       <c r="C6">
-        <v>5317094333.2703209</v>
+        <v>4814187796.8760338</v>
       </c>
     </row>
     <row r="7">
@@ -1783,7 +1783,7 @@
         <v>131000000000000</v>
       </c>
       <c r="C7">
-        <v>102281844002.70367</v>
+        <v>92607724139.612396</v>
       </c>
     </row>
     <row r="8">
@@ -1794,7 +1794,7 @@
         <v>224000000000000</v>
       </c>
       <c r="C8">
-        <v>174894145470.27197</v>
+        <v>158352138986.81818</v>
       </c>
     </row>
     <row r="9">
@@ -1805,7 +1805,7 @@
         <v>5810000000</v>
       </c>
       <c r="C9">
-        <v>4536316.8981351787</v>
+        <v>4107258.6049705963</v>
       </c>
     </row>
     <row r="10">
@@ -1816,7 +1816,7 @@
         <v>201000000000</v>
       </c>
       <c r="C10">
-        <v>156936264.46216366</v>
+        <v>142092767.57299307</v>
       </c>
     </row>
     <row r="11">
@@ -1827,7 +1827,7 @@
         <v>6130000000000</v>
       </c>
       <c r="C11">
-        <v>4786165677.3784246</v>
+        <v>4333475946.3803368</v>
       </c>
     </row>
     <row r="12">
@@ -1838,7 +1838,7 @@
         <v>962000</v>
       </c>
       <c r="C12">
-        <v>751.10789260000718</v>
+        <v>680.06588261303148</v>
       </c>
     </row>
     <row r="13">
@@ -1849,7 +1849,7 @@
         <v>4100000</v>
       </c>
       <c r="C13">
-        <v>3201.187484054085</v>
+        <v>2898.409686812297</v>
       </c>
     </row>
     <row r="14">
@@ -1860,7 +1860,7 @@
         <v>527000000000000</v>
       </c>
       <c r="C14">
-        <v>411469708316.22021</v>
+        <v>372551684134.16595</v>
       </c>
     </row>
     <row r="15">
@@ -1871,7 +1871,7 @@
         <v>5210000000000000</v>
       </c>
       <c r="C15">
-        <v>4067850437054.0933</v>
+        <v>3683101089827.3335</v>
       </c>
     </row>
     <row r="16">
@@ -1882,7 +1882,7 @@
         <v>219000000</v>
       </c>
       <c r="C16">
-        <v>170990.25829459622</v>
+        <v>154817.49302729097</v>
       </c>
     </row>
     <row r="17">
@@ -1893,7 +1893,7 @@
         <v>539000000</v>
       </c>
       <c r="C17">
-        <v>420839.03753784188</v>
+        <v>381034.83443703118</v>
       </c>
     </row>
     <row r="18">
@@ -1904,7 +1904,7 @@
         <v>516000</v>
       </c>
       <c r="C18">
-        <v>402.88115652973363</v>
+        <v>364.77546302320616</v>
       </c>
     </row>
     <row r="19">
@@ -1915,7 +1915,7 @@
         <v>407000000000</v>
       </c>
       <c r="C19">
-        <v>317776416.10000306</v>
+        <v>287720181.10551333</v>
       </c>
     </row>
     <row r="20">
@@ -1926,7 +1926,7 @@
         <v>182000000000000</v>
       </c>
       <c r="C20">
-        <v>142101493194.59595</v>
+        <v>128661112926.78975</v>
       </c>
     </row>
   </sheetData>
